--- a/Sample Data.xlsx
+++ b/Sample Data.xlsx
@@ -1,18 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cameron\Documents\Repos\Excel-Sheets-Transform-\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sample" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Changed data" sheetId="2" r:id="rId5"/>
+    <sheet name="Sample" sheetId="1" r:id="rId1"/>
+    <sheet name="Changed data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t xml:space="preserve">Sample </t>
   </si>
@@ -147,6 +153,9 @@
   </si>
   <si>
     <t xml:space="preserve">lowest </t>
+  </si>
+  <si>
+    <t>test2</t>
   </si>
   <si>
     <t>6a</t>
@@ -164,20 +173,23 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="5">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="9"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -185,11 +197,13 @@
     <font>
       <b/>
       <i/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF46BDC6"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -200,131 +214,92 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFCCA677"/>
           <bgColor rgb="FFCCA677"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8F2EB"/>
           <bgColor rgb="FFF8F2EB"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
   </dxfs>
   <tableStyles count="2">
-    <tableStyle count="3" pivot="0" name="Sample-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Sample-style" pivot="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="0"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Changed data-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Changed data-style" pivot="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="0"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="I8:K8" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_1" displayName="Table_1" ref="I8:K8" headerRowCount="0">
   <tableColumns count="3">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
   </tableColumns>
   <tableStyleInfo name="Sample-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
-    </ext>
-  </extLst>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="H8:K8" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table_2" displayName="Table_2" ref="H8:K8" headerRowCount="0">
   <tableColumns count="4">
-    <tableColumn name="Column1" id="1"/>
-    <tableColumn name="Column2" id="2"/>
-    <tableColumn name="Column3" id="3"/>
-    <tableColumn name="Column4" id="4"/>
+    <tableColumn id="1" name="Column1"/>
+    <tableColumn id="2" name="Column2"/>
+    <tableColumn id="3" name="Column3"/>
+    <tableColumn id="4" name="Column4"/>
   </tableColumns>
   <tableStyleInfo name="Changed data-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
-    </ext>
-  </extLst>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -406,6 +381,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -432,24 +408,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -510,6 +487,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -518,18 +496,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -561,9 +539,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -587,19 +565,19 @@
         <v>16</v>
       </c>
       <c r="I3" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="J3" s="1">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="K3" s="3">
-        <f t="shared" ref="K3:K8" si="1">SUM(I3:J3)</f>
+        <f t="shared" ref="K3:K8" si="0">SUM(I3:J3)</f>
         <v>78</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>17</v>
@@ -623,19 +601,19 @@
         <v>22</v>
       </c>
       <c r="I4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="J4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="K4" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>23</v>
@@ -659,19 +637,19 @@
         <v>28</v>
       </c>
       <c r="I5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="J5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="K5" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>29</v>
@@ -695,19 +673,19 @@
         <v>34</v>
       </c>
       <c r="I6" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="J6" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>35</v>
@@ -731,84 +709,175 @@
         <v>40</v>
       </c>
       <c r="I7" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="J7" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="K7" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="F8" s="1"/>
       <c r="I8" s="4">
-        <f t="shared" ref="I8:J8" si="2">SUM(I2:I7)</f>
+        <f t="shared" ref="I8:J8" si="1">SUM(I2:I7)</f>
         <v>21</v>
       </c>
       <c r="J8" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>85</v>
       </c>
       <c r="K8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>106</v>
       </c>
     </row>
-    <row r="17">
-      <c r="H17" s="1" t="s">
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="C14" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18">
-      <c r="G18" s="1" t="s">
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="B15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="1">
-        <v>101.0</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="C15" s="1">
+        <v>101</v>
+      </c>
+      <c r="D15" s="3">
         <f>SUM(K3:K7)</f>
         <v>106</v>
       </c>
     </row>
-    <row r="19">
-      <c r="G19" s="1" t="s">
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="B16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="I19" s="3">
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3">
         <f>MIN(J3:J7)</f>
         <v>2</v>
       </c>
     </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="B20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1">
+        <v>101</v>
+      </c>
+      <c r="D20" s="3">
+        <f>SUM(K8:K12)</f>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="B21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="3">
+        <f>MIN(J8:J12)</f>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="B25" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="1">
+        <v>101</v>
+      </c>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="B26" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26" s="1">
+        <v>3</v>
+      </c>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="B29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="B30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="1"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="B32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" s="1">
+        <v>101</v>
+      </c>
+      <c r="D32" s="3">
+        <f>SUM(K20:K24)</f>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -840,9 +909,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -854,7 +923,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="1">
-        <v>71.0</v>
+        <v>71</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>13</v>
@@ -863,7 +932,7 @@
         <v>14</v>
       </c>
       <c r="H3" s="1">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>15</v>
@@ -872,13 +941,13 @@
         <v>16</v>
       </c>
       <c r="K3" s="3">
-        <f t="shared" ref="K3:K8" si="1">SUM(H3:J3)</f>
+        <f t="shared" ref="K3:K8" si="0">SUM(H3:J3)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>17</v>
@@ -890,7 +959,7 @@
         <v>18</v>
       </c>
       <c r="E4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>19</v>
@@ -899,7 +968,7 @@
         <v>20</v>
       </c>
       <c r="H4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>21</v>
@@ -908,13 +977,13 @@
         <v>22</v>
       </c>
       <c r="K4" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>23</v>
@@ -926,7 +995,7 @@
         <v>24</v>
       </c>
       <c r="E5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>25</v>
@@ -935,7 +1004,7 @@
         <v>26</v>
       </c>
       <c r="H5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>27</v>
@@ -944,13 +1013,13 @@
         <v>28</v>
       </c>
       <c r="K5" s="3">
-        <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>29</v>
@@ -962,7 +1031,7 @@
         <v>30</v>
       </c>
       <c r="E6" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>31</v>
@@ -971,7 +1040,7 @@
         <v>32</v>
       </c>
       <c r="H6" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>33</v>
@@ -980,13 +1049,13 @@
         <v>34</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>35</v>
@@ -998,7 +1067,7 @@
         <v>36</v>
       </c>
       <c r="E7" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>37</v>
@@ -1007,7 +1076,7 @@
         <v>38</v>
       </c>
       <c r="H7" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>39</v>
@@ -1016,34 +1085,34 @@
         <v>40</v>
       </c>
       <c r="K7" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E8" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H8" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>39</v>
@@ -1052,11 +1121,11 @@
         <v>40</v>
       </c>
       <c r="K8" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="C12" s="1" t="s">
         <v>41</v>
       </c>
@@ -1064,24 +1133,24 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="B13" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="1">
-        <v>101.0</v>
+        <v>101</v>
       </c>
       <c r="D13" s="3" t="str">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D14" s="3" t="str">
         <f>MIN(#REF!)</f>
@@ -1089,9 +1158,8 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>